--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -203,10 +203,10 @@
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>NC</t>
@@ -1016,22 +1016,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1055,13 +1055,13 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1093,22 +1093,22 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1138,13 +1138,13 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1173,13 +1173,13 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1247,22 +1247,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1286,13 +1286,13 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>8</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1327,16 +1327,16 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1369,7 +1369,7 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1401,22 +1401,22 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1437,10 +1437,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1478,22 +1478,22 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1523,7 +1523,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1555,22 +1555,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1591,10 +1591,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1603,7 +1603,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1632,22 +1632,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1712,19 +1712,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1786,22 +1786,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1822,10 +1822,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -1863,22 +1863,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1908,7 +1908,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1940,22 +1940,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2017,22 +2017,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2097,19 +2097,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2165,22 +2165,22 @@
         <v>7</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2216,13 +2216,13 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2248,22 +2248,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2284,7 +2284,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2325,22 +2325,22 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2361,7 +2361,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2402,22 +2402,22 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2488,13 +2488,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2524,7 +2524,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2559,16 +2559,16 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2633,22 +2633,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2669,7 +2669,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2678,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2710,22 +2710,22 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2796,13 +2796,13 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2832,7 +2832,7 @@
         <v>6</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2864,19 +2864,19 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2900,7 +2900,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2909,7 +2909,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2944,16 +2944,16 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2986,7 +2986,7 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3021,19 +3021,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3063,7 +3063,7 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -3098,19 +3098,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3140,7 +3140,7 @@
         <v>7</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3172,22 +3172,22 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3211,13 +3211,13 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3249,22 +3249,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3285,7 +3285,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3294,7 +3294,7 @@
         <v>6</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3326,22 +3326,22 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3371,7 +3371,7 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3406,19 +3406,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3448,7 +3448,7 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3480,22 +3480,22 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3525,7 +3525,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3557,22 +3557,22 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3596,13 +3596,13 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>9</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3634,22 +3634,22 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3711,22 +3711,22 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3750,13 +3750,13 @@
         <v>9</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>8</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -3791,16 +3791,16 @@
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3833,7 +3833,7 @@
         <v>5</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -4000,62 +4000,62 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>37</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4092,7 +4092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4201,56 +4201,56 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920168</v>
+        <v>20330051920173</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920168</v>
+        <v>20330051920173</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4261,56 +4261,56 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920173</v>
+        <v>20330051920178</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920174</v>
+        <v>20330051920178</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920178</v>
+        <v>20330051920180</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -4321,36 +4321,36 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920178</v>
+        <v>20330051920373</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920180</v>
+        <v>20330051920145</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -4361,16 +4361,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920373</v>
+        <v>20330051920182</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -4381,61 +4381,21 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920145</v>
+        <v>20330051920388</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920182</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920388</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4472,33 +4432,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920168</v>
+        <v>20330051920173</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920173</v>
+        <v>20330051920178</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -4506,33 +4466,33 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920178</v>
+        <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920157</v>
+        <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4540,16 +4500,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920158</v>
+        <v>20330051920164</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4557,16 +4517,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920164</v>
+        <v>20330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -5106,7 +5066,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5276,16 +5236,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920174</v>
+        <v>20330051920168</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5299,16 +5259,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920174</v>
+        <v>20330051920168</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5322,16 +5282,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920178</v>
+        <v>20330051920174</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5345,39 +5305,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920178</v>
+        <v>20330051920174</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920182</v>
+        <v>20330051920178</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -5391,39 +5351,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920182</v>
+        <v>20330051920178</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920388</v>
+        <v>20330051920182</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -5437,16 +5397,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920388</v>
+        <v>20330051920182</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -5460,16 +5420,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920180</v>
+        <v>20330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -5483,39 +5443,39 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920373</v>
+        <v>20330051920388</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17">
         <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920145</v>
+        <v>20330051920180</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -5524,6 +5484,52 @@
         <v>58</v>
       </c>
       <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920373</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920145</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -1185,7 +1185,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1221,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1339,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1375,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -2491,7 +2491,7 @@
         <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -2527,7 +2527,7 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2571,7 +2571,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2607,7 +2607,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2879,7 +2879,7 @@
         <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2956,7 +2956,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2992,7 +2992,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3803,7 +3803,7 @@
         <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3839,7 +3839,7 @@
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4044,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -1182,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -2183,10 +2183,10 @@
         <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -1099,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>9</v>
@@ -1176,7 +1176,7 @@
         <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -1253,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -1330,7 +1330,7 @@
         <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>9</v>
@@ -1407,7 +1407,7 @@
         <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -1443,7 +1443,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1484,7 +1484,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>9</v>
@@ -1561,7 +1561,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>9</v>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1638,7 +1638,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>9</v>
@@ -1715,7 +1715,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -1792,7 +1792,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>9</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1946,7 +1946,7 @@
         <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>9</v>
@@ -2023,7 +2023,7 @@
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -2059,7 +2059,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2100,7 +2100,7 @@
         <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>9</v>
@@ -2136,7 +2136,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2177,7 +2177,7 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>9</v>
@@ -2254,7 +2254,7 @@
         <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>9</v>
@@ -2331,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -2408,7 +2408,7 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>9</v>
@@ -2485,7 +2485,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -2562,7 +2562,7 @@
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -2639,7 +2639,7 @@
         <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>9</v>
@@ -2675,7 +2675,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2716,7 +2716,7 @@
         <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -2793,7 +2793,7 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>9</v>
@@ -2870,7 +2870,7 @@
         <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>9</v>
@@ -2947,7 +2947,7 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
         <v>9</v>
@@ -3024,7 +3024,7 @@
         <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>9</v>
@@ -3101,7 +3101,7 @@
         <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>9</v>
@@ -3178,7 +3178,7 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>9</v>
@@ -3255,7 +3255,7 @@
         <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>9</v>
@@ -3291,7 +3291,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3332,7 +3332,7 @@
         <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
         <v>9</v>
@@ -3368,7 +3368,7 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3409,7 +3409,7 @@
         <v>7</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>9</v>
@@ -3486,7 +3486,7 @@
         <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>9</v>
@@ -3522,7 +3522,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -3563,7 +3563,7 @@
         <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
         <v>9</v>
@@ -3640,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>9</v>
@@ -3717,7 +3717,7 @@
         <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
         <v>9</v>
@@ -3794,7 +3794,7 @@
         <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>9</v>
@@ -3948,7 +3948,7 @@
         <v>21.62</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
@@ -221,25 +221,97 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
     <t>HUESCA</t>
   </si>
   <si>
-    <t>MENDEZ</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MATA</t>
   </si>
   <si>
     <t>NAMORADO</t>
   </si>
   <si>
-    <t>QUIRIZ</t>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>RIVERA</t>
@@ -251,58 +323,163 @@
     <t>RUIZ</t>
   </si>
   <si>
-    <t>TORRES</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
   </si>
   <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>MELO</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
     <t>DINA BERENICE</t>
   </si>
   <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
     <t>AISHA NAOMI</t>
   </si>
   <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
     <t>ALDAIR OMAR</t>
   </si>
   <si>
-    <t>VANNIA GISELLE</t>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
   </si>
   <si>
     <t>LUZ ESTRELLA</t>
   </si>
   <si>
-    <t>MONICA</t>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>IDETH JOSELYN</t>
+  </si>
+  <si>
+    <t>ESTHER ARISBETH</t>
   </si>
   <si>
     <t>JAROMI YAJAIRA</t>
@@ -314,205 +491,28 @@
     <t>XIMENA MICHELL</t>
   </si>
   <si>
-    <t>DIEGO</t>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>IRIS VIANNEY</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
+  </si>
+  <si>
+    <t>EVELYN IVETH</t>
+  </si>
+  <si>
+    <t>MARIAN</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>AYARI</t>
   </si>
   <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
-    <t>ESTHER ARISBETH</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>IRIS VIANNEY</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>EVELYN IVETH</t>
-  </si>
-  <si>
-    <t>MARIAN</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>AYARI</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1152,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -1170,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1306,7 +1306,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1324,7 +1324,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -1360,7 +1360,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1691,7 +1691,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1709,7 +1709,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -1745,7 +1745,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -2094,7 +2094,7 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -2130,7 +2130,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2153,7 +2153,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -2171,7 +2171,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -2207,7 +2207,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2461,7 +2461,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>-1</v>
@@ -2479,7 +2479,7 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2515,7 +2515,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2538,7 +2538,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -2592,7 +2592,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2769,7 +2769,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>-1</v>
@@ -2787,7 +2787,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2823,7 +2823,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2923,7 +2923,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -2941,7 +2941,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -2977,7 +2977,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -3000,7 +3000,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -3018,7 +3018,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -3054,7 +3054,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -3077,7 +3077,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -3095,7 +3095,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -3131,7 +3131,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -3770,7 +3770,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -3788,7 +3788,7 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -3824,7 +3824,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>7</v>
@@ -3895,7 +3895,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -3904,30 +3904,30 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>67.56999999999999</v>
+        <v>78.38</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>21.62</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>32.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -3936,25 +3936,25 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>78.38</v>
+        <v>81.08</v>
       </c>
       <c r="G3">
-        <v>21.62</v>
+        <v>16.22</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4092,7 +4092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4121,282 +4121,62 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920157</v>
+        <v>20330051920173</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920158</v>
+        <v>20330051920178</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920164</v>
+        <v>20330051920182</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920173</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920173</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920174</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920178</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920178</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920180</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920373</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920145</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920182</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920388</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4435,16 +4215,16 @@
         <v>20330051920173</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4452,30 +4232,30 @@
         <v>20330051920178</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920157</v>
+        <v>20330051920182</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4483,166 +4263,166 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920158</v>
+        <v>20330051920368</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920164</v>
+        <v>20330051920156</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920168</v>
+        <v>20330051920157</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920174</v>
+        <v>20330051920158</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920180</v>
+        <v>20330051920369</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920373</v>
+        <v>20330051920160</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920145</v>
+        <v>20330051920161</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920182</v>
+        <v>20330051920162</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920388</v>
+        <v>20330051920163</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920368</v>
+        <v>20330051920164</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
         <v>140</v>
@@ -4653,13 +4433,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920156</v>
+        <v>20330051920370</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
         <v>141</v>
@@ -4670,13 +4450,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920369</v>
+        <v>20330051920372</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
         <v>142</v>
@@ -4687,13 +4467,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920160</v>
+        <v>20330051920165</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
         <v>143</v>
@@ -4704,13 +4484,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920161</v>
+        <v>20330051920167</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
         <v>144</v>
@@ -4721,13 +4501,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920162</v>
+        <v>20330051920166</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -4738,13 +4518,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920163</v>
+        <v>20330051920168</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
@@ -4755,13 +4535,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920370</v>
+        <v>20330051920371</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
@@ -4772,13 +4552,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920372</v>
+        <v>20330051920171</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
         <v>148</v>
@@ -4789,13 +4569,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920165</v>
+        <v>20330051920172</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -4806,13 +4586,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920167</v>
+        <v>20330051920174</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
@@ -4823,13 +4603,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920166</v>
+        <v>20330051920306</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
@@ -4840,13 +4620,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920371</v>
+        <v>20330051920177</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
@@ -4857,13 +4637,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920171</v>
+        <v>20330051920179</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
@@ -4874,13 +4654,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920172</v>
+        <v>20330051920180</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -4891,13 +4671,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920306</v>
+        <v>20330051920373</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -4908,13 +4688,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920177</v>
+        <v>20330051920145</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -4925,13 +4705,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920179</v>
+        <v>20330051920254</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -4942,13 +4722,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920254</v>
+        <v>20330051920181</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -4959,13 +4739,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920181</v>
+        <v>20330051920393</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -4976,13 +4756,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920393</v>
+        <v>20330051920183</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -4993,13 +4773,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920183</v>
+        <v>20330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -5010,13 +4790,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920184</v>
+        <v>20330051920154</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -5027,13 +4807,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920154</v>
+        <v>20330051920186</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
@@ -5044,13 +4824,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>20330051920186</v>
+        <v>20330051920388</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
@@ -5066,7 +4846,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5101,22 +4881,22 @@
         <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5124,19 +4904,19 @@
         <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5147,22 +4927,22 @@
         <v>20330051920158</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5170,19 +4950,19 @@
         <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5190,45 +4970,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920164</v>
+        <v>20330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920164</v>
+        <v>20330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5236,22 +5016,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920168</v>
+        <v>20330051920173</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>70</v>
       </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -5259,22 +5039,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920168</v>
+        <v>20330051920173</v>
       </c>
       <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5285,22 +5065,22 @@
         <v>20330051920174</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5308,19 +5088,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5331,22 +5111,22 @@
         <v>20330051920178</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5354,13 +5134,13 @@
         <v>20330051920178</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -5377,19 +5157,19 @@
         <v>20330051920182</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -5400,19 +5180,19 @@
         <v>20330051920182</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5423,22 +5203,22 @@
         <v>20330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5446,19 +5226,19 @@
         <v>20330051920388</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -5466,71 +5246,25 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920180</v>
+        <v>20330051920164</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
         <v>58</v>
       </c>
       <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920373</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920145</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -200,12 +200,12 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
@@ -221,262 +221,262 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>QUIRIZ</t>
   </si>
   <si>
-    <t>TORRES</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>MELO</t>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
   </si>
   <si>
     <t>VANNIA GISELLE</t>
   </si>
   <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>IDETH JOSELYN</t>
+  </si>
+  <si>
     <t>MONICA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>IDETH JOSELYN</t>
   </si>
   <si>
     <t>ESTHER ARISBETH</t>
@@ -2464,7 +2464,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -2482,7 +2482,7 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -2518,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2772,7 +2772,7 @@
         <v>5</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2790,7 +2790,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>6</v>
@@ -2826,7 +2826,7 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
@@ -3968,30 +3968,30 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>5.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4092,7 +4092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4121,61 +4121,21 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920173</v>
+        <v>20330051920182</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920178</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920182</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4212,16 +4172,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920173</v>
+        <v>20330051920182</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -4229,47 +4189,47 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920178</v>
+        <v>20330051920368</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920182</v>
+        <v>20330051920156</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920368</v>
+        <v>20330051920157</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
         <v>131</v>
@@ -4280,13 +4240,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920156</v>
+        <v>20330051920158</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
         <v>132</v>
@@ -4297,13 +4257,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920157</v>
+        <v>20330051920369</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
@@ -4314,13 +4274,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920158</v>
+        <v>20330051920160</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
         <v>134</v>
@@ -4331,13 +4291,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920369</v>
+        <v>20330051920161</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
         <v>135</v>
@@ -4348,13 +4308,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920160</v>
+        <v>20330051920162</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
         <v>136</v>
@@ -4365,13 +4325,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920161</v>
+        <v>20330051920163</v>
       </c>
       <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
         <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>112</v>
       </c>
       <c r="D11" t="s">
         <v>137</v>
@@ -4382,13 +4342,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920162</v>
+        <v>20330051920164</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
         <v>138</v>
@@ -4399,13 +4359,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920163</v>
+        <v>20330051920370</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
         <v>139</v>
@@ -4416,13 +4376,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920164</v>
+        <v>20330051920372</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
         <v>140</v>
@@ -4433,13 +4393,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920370</v>
+        <v>20330051920165</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
         <v>141</v>
@@ -4450,13 +4410,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920372</v>
+        <v>20330051920167</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
         <v>142</v>
@@ -4467,13 +4427,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920165</v>
+        <v>20330051920166</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
         <v>143</v>
@@ -4484,13 +4444,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920167</v>
+        <v>20330051920168</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
         <v>144</v>
@@ -4501,13 +4461,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920166</v>
+        <v>20330051920371</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -4518,13 +4478,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920168</v>
+        <v>20330051920171</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
@@ -4535,13 +4495,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920371</v>
+        <v>20330051920172</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
@@ -4552,13 +4512,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920171</v>
+        <v>20330051920173</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
         <v>148</v>
@@ -4569,13 +4529,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920172</v>
+        <v>20330051920174</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -4586,13 +4546,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920174</v>
+        <v>20330051920306</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
@@ -4603,13 +4563,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920306</v>
+        <v>20330051920177</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
@@ -4620,13 +4580,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920177</v>
+        <v>20330051920178</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
@@ -4640,10 +4600,10 @@
         <v>20330051920179</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
@@ -4657,10 +4617,10 @@
         <v>20330051920180</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -4674,10 +4634,10 @@
         <v>20330051920373</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -4691,10 +4651,10 @@
         <v>20330051920145</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -4708,10 +4668,10 @@
         <v>20330051920254</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -4725,10 +4685,10 @@
         <v>20330051920181</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -4742,10 +4702,10 @@
         <v>20330051920393</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -4759,10 +4719,10 @@
         <v>20330051920183</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -4776,10 +4736,10 @@
         <v>20330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -4793,10 +4753,10 @@
         <v>20330051920154</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -4810,10 +4770,10 @@
         <v>20330051920186</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
@@ -4827,10 +4787,10 @@
         <v>20330051920388</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
@@ -4846,7 +4806,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4881,13 +4841,13 @@
         <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4904,13 +4864,13 @@
         <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4927,13 +4887,13 @@
         <v>20330051920158</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4950,13 +4910,13 @@
         <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4973,13 +4933,13 @@
         <v>20330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -4996,13 +4956,13 @@
         <v>20330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5016,39 +4976,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5062,16 +5022,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920174</v>
+        <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5080,21 +5040,21 @@
         <v>59</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920174</v>
+        <v>20330051920182</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5108,16 +5068,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920178</v>
+        <v>20330051920388</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -5131,62 +5091,62 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920178</v>
+        <v>20330051920388</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920182</v>
+        <v>20330051920164</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920182</v>
+        <v>20330051920173</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -5200,16 +5160,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920388</v>
+        <v>20330051920178</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -5218,52 +5178,6 @@
         <v>59</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920388</v>
-      </c>
-      <c r="B17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920164</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -1034,16 +1034,16 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1111,16 +1111,16 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1188,16 +1188,16 @@
         <v>4</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1265,16 +1265,16 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1342,16 +1342,16 @@
         <v>4</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1360,7 +1360,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1419,16 +1419,16 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1496,16 +1496,16 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1514,7 +1514,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1573,16 +1573,16 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1591,7 +1591,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1650,16 +1650,16 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1668,10 +1668,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1727,16 +1727,16 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1745,7 +1745,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1804,16 +1804,16 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1881,16 +1881,16 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1902,7 +1902,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1958,16 +1958,16 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2035,16 +2035,16 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2112,16 +2112,16 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2189,16 +2189,16 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2266,16 +2266,16 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2287,7 +2287,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2343,16 +2343,16 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2364,7 +2364,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2420,16 +2420,16 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2438,7 +2438,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2497,16 +2497,16 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2515,7 +2515,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2574,16 +2574,16 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2592,10 +2592,10 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2651,16 +2651,16 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2728,16 +2728,16 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2749,7 +2749,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2805,16 +2805,16 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2823,7 +2823,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2882,16 +2882,16 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2900,7 +2900,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2959,16 +2959,16 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3036,16 +3036,16 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3054,7 +3054,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -3113,16 +3113,16 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3134,7 +3134,7 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -3190,16 +3190,16 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3267,16 +3267,16 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3285,7 +3285,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3344,16 +3344,16 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3424,13 +3424,13 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3498,16 +3498,16 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3516,7 +3516,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>8</v>
@@ -3575,16 +3575,16 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3652,16 +3652,16 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3670,7 +3670,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>8</v>
@@ -3729,16 +3729,16 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3747,7 +3747,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>8</v>
@@ -3806,16 +3806,16 @@
         <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3824,7 +3824,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U40">
         <v>7</v>
@@ -3936,19 +3936,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>81.08</v>
+        <v>94.59</v>
       </c>
       <c r="G3">
-        <v>16.22</v>
+        <v>2.7</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4806,7 +4806,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4838,16 +4838,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920157</v>
+        <v>20330051920168</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4861,16 +4861,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920157</v>
+        <v>20330051920168</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4884,16 +4884,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920158</v>
+        <v>20330051920182</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4902,21 +4902,21 @@
         <v>59</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920158</v>
+        <v>20330051920182</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4930,22 +4930,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920168</v>
+        <v>20330051920157</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4953,16 +4953,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920168</v>
+        <v>20330051920158</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920174</v>
+        <v>20330051920164</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
         <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4999,16 +4999,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920174</v>
+        <v>20330051920173</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5022,39 +5022,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920182</v>
+        <v>20330051920174</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
         <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920182</v>
+        <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5063,121 +5063,6 @@
         <v>58</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920388</v>
-      </c>
-      <c r="B12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920388</v>
-      </c>
-      <c r="B13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" t="s">
-        <v>164</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920164</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920173</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920178</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" t="s">
-        <v>152</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -1046,10 +1046,10 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -1123,10 +1123,10 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1141,10 +1141,10 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1200,10 +1200,10 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1221,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1277,10 +1277,10 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1354,10 +1354,10 @@
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>6</v>
@@ -1431,10 +1431,10 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1508,10 +1508,10 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1585,10 +1585,10 @@
         <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1603,7 +1603,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1662,10 +1662,10 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1739,10 +1739,10 @@
         <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1816,10 +1816,10 @@
         <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1893,10 +1893,10 @@
         <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1970,10 +1970,10 @@
         <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -2047,10 +2047,10 @@
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2124,10 +2124,10 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -2201,10 +2201,10 @@
         <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -2278,10 +2278,10 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2355,10 +2355,10 @@
         <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2509,10 +2509,10 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2530,7 +2530,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2586,10 +2586,10 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2604,7 +2604,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2663,10 +2663,10 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2740,10 +2740,10 @@
         <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2817,7 +2817,7 @@
         <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2835,7 +2835,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2894,10 +2894,10 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2912,10 +2912,10 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2971,10 +2971,10 @@
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -3051,7 +3051,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -3125,10 +3125,10 @@
         <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3202,10 +3202,10 @@
         <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3279,10 +3279,10 @@
         <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3356,10 +3356,10 @@
         <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -3433,10 +3433,10 @@
         <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>-1</v>
@@ -3451,7 +3451,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3510,10 +3510,10 @@
         <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3528,7 +3528,7 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3587,10 +3587,10 @@
         <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3664,10 +3664,10 @@
         <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3741,10 +3741,10 @@
         <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -3818,10 +3818,10 @@
         <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T40">
         <v>6</v>
@@ -3839,7 +3839,7 @@
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4044,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -2432,10 +2432,10 @@
         <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2820,7 +2820,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>6</v>
@@ -2838,7 +2838,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">

--- a/grupos/5ARHM - Estadisticos 20221.xlsx
+++ b/grupos/5ARHM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -221,283 +221,283 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>MELO</t>
   </si>
   <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>IDETH JOSELYN</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>ESTHER ARISBETH</t>
+  </si>
+  <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>IRIS VIANNEY</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>ESTHER ARISBETH</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>IRIS VIANNEY</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
   </si>
   <si>
     <t>EVELYN IVETH</t>
@@ -1040,7 +1040,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -1117,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1194,7 +1194,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -1212,7 +1212,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1271,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1289,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1348,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1366,7 +1366,7 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1425,7 +1425,7 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1502,7 +1502,7 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -1579,7 +1579,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1656,7 +1656,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -1674,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1733,7 +1733,7 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1751,7 +1751,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1810,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1887,7 +1887,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1964,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2059,7 +2059,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2118,7 +2118,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2195,7 +2195,7 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>9</v>
@@ -2272,7 +2272,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2349,7 +2349,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2426,7 +2426,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -2503,7 +2503,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2580,7 +2580,7 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2598,7 +2598,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2657,7 +2657,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2734,7 +2734,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2811,7 +2811,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>9</v>
@@ -2888,7 +2888,7 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2965,7 +2965,7 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>9</v>
@@ -2983,7 +2983,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3042,13 +3042,13 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>9</v>
@@ -3119,7 +3119,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3196,7 +3196,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -3273,7 +3273,7 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -3350,7 +3350,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3385,7 +3385,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>7</v>
@@ -3403,7 +3403,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>7</v>
@@ -3421,13 +3421,13 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3439,13 +3439,13 @@
         <v>8</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>7</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3504,7 +3504,7 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -3581,7 +3581,7 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -3658,7 +3658,7 @@
         <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -3676,7 +3676,7 @@
         <v>8</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>9</v>
@@ -3735,7 +3735,7 @@
         <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>9</v>
@@ -3812,7 +3812,7 @@
         <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>7</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3895,7 +3895,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -3904,19 +3904,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>78.38</v>
+        <v>94.59</v>
       </c>
       <c r="G2">
-        <v>21.62</v>
+        <v>5.41</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3927,7 +3927,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -3936,25 +3936,25 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>94.59</v>
+        <v>97.3</v>
       </c>
       <c r="G3">
         <v>2.7</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4092,7 +4092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4117,26 +4117,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920182</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4172,30 +4152,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920182</v>
+        <v>20330051920368</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920368</v>
+        <v>20330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
         <v>129</v>
@@ -4206,13 +4186,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920156</v>
+        <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
         <v>130</v>
@@ -4223,13 +4203,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920157</v>
+        <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
         <v>131</v>
@@ -4240,13 +4220,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920158</v>
+        <v>20330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
         <v>132</v>
@@ -4257,13 +4237,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920369</v>
+        <v>20330051920160</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
@@ -4274,13 +4254,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920160</v>
+        <v>20330051920161</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
         <v>134</v>
@@ -4291,13 +4271,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920161</v>
+        <v>20330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
         <v>135</v>
@@ -4308,13 +4288,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920162</v>
+        <v>20330051920163</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>136</v>
@@ -4325,13 +4305,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920163</v>
+        <v>20330051920164</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
         <v>137</v>
@@ -4342,13 +4322,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920164</v>
+        <v>20330051920370</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
         <v>138</v>
@@ -4359,13 +4339,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920370</v>
+        <v>20330051920372</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
         <v>139</v>
@@ -4376,13 +4356,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920372</v>
+        <v>20330051920165</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
         <v>140</v>
@@ -4393,13 +4373,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920165</v>
+        <v>20330051920167</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
         <v>141</v>
@@ -4410,13 +4390,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920167</v>
+        <v>20330051920166</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
         <v>142</v>
@@ -4427,13 +4407,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920166</v>
+        <v>20330051920168</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
         <v>143</v>
@@ -4444,13 +4424,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920168</v>
+        <v>20330051920371</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
         <v>144</v>
@@ -4461,13 +4441,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920371</v>
+        <v>20330051920171</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -4478,13 +4458,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920171</v>
+        <v>20330051920172</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
@@ -4495,13 +4475,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920172</v>
+        <v>20330051920173</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
@@ -4512,13 +4492,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
         <v>148</v>
@@ -4529,13 +4509,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920174</v>
+        <v>20330051920306</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -4546,13 +4526,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920306</v>
+        <v>20330051920177</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
@@ -4563,13 +4543,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920177</v>
+        <v>20330051920178</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
@@ -4580,13 +4560,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920178</v>
+        <v>20330051920179</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
@@ -4597,13 +4577,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920179</v>
+        <v>20330051920180</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
@@ -4614,13 +4594,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920180</v>
+        <v>20330051920373</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -4631,13 +4611,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920373</v>
+        <v>20330051920145</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -4648,13 +4628,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920145</v>
+        <v>20330051920254</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -4665,13 +4645,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920254</v>
+        <v>20330051920181</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -4682,13 +4662,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920181</v>
+        <v>20330051920393</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -4699,13 +4679,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920393</v>
+        <v>20330051920182</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -4719,10 +4699,10 @@
         <v>20330051920183</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -4736,10 +4716,10 @@
         <v>20330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -4753,10 +4733,10 @@
         <v>20330051920154</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -4770,10 +4750,10 @@
         <v>20330051920186</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
@@ -4787,10 +4767,10 @@
         <v>20330051920388</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
@@ -4806,7 +4786,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4841,19 +4821,19 @@
         <v>20330051920168</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4864,19 +4844,19 @@
         <v>20330051920168</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4887,182 +4867,21 @@
         <v>20330051920182</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920182</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920157</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920158</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920164</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920173</v>
-      </c>
-      <c r="B9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920174</v>
-      </c>
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920388</v>
-      </c>
-      <c r="B11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" t="s">
-        <v>164</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>
